--- a/data/processed_data/Video_prueba/contracciones.xlsx
+++ b/data/processed_data/Video_prueba/contracciones.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="estab_Video_prueba" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="resumen_Video_prueba" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ritmo_Video_prueba" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="grilla_Video_prueba" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="espont_Video_prueba" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="poblac_Video_prueba" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="eventos_Video_prueba" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="estab_Video_prueba" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resumen_Video_prueba" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ritmo_Video_prueba" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="grilla_Video_prueba" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="espont_Video_prueba" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="poblac_Video_prueba" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eventos_Video_prueba" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,16 +23,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -51,21 +48,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,22 +423,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>umbral_px</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>eventos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>falsos_control</t>
         </is>
@@ -461,10 +449,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>0.258</v>
+        <v>0.2562</v>
       </c>
       <c r="C2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -475,10 +463,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>0.344</v>
+        <v>0.3416</v>
       </c>
       <c r="C3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -489,10 +477,10 @@
         <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5159</v>
+        <v>0.5124</v>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -503,10 +491,10 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6879</v>
+        <v>0.6832</v>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -517,10 +505,10 @@
         <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8599</v>
+        <v>0.854</v>
       </c>
       <c r="C6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -531,10 +519,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>1.0319</v>
+        <v>1.0248</v>
       </c>
       <c r="C7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -545,10 +533,10 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>1.2899</v>
+        <v>1.281</v>
       </c>
       <c r="C8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -559,7 +547,7 @@
         <v>20</v>
       </c>
       <c r="B9" t="n">
-        <v>1.7198</v>
+        <v>1.708</v>
       </c>
       <c r="C9" t="n">
         <v>26</v>
@@ -579,111 +567,141 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_frames</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>signo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ruido_canal_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ruido_grosor_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>k_usado</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>k_automatico</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>hay_meseta</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>meseta_motivo</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>meseta_k_rango</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>conteo_reportable</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>amplitud_traslacion_px</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ritmo</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>fps_medido</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>adelgazamiento_px</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>adelgazamiento_sigma</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>retardo_adelgazamiento_s</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cociente_adelg_trasl_pct</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_px</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_sigma</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>cociente_robusto_pct</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>blur_px</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>blur_sigma</t>
         </is>
@@ -696,99 +714,119 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.72892904755024</v>
+        <v>30.00000000000171</v>
       </c>
       <c r="C2" t="n">
         <v>2007</v>
       </c>
       <c r="D2" t="n">
-        <v>67.47636273044344</v>
+        <v>67.47500000000001</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08599079999998921</v>
+        <v>0.08539776000005379</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08935370202174786</v>
+        <v>0.09005957368569244</v>
       </c>
       <c r="H2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5718335824613854</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.083199999999977</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>{'n_eventos': 29, 'hay_estimulacion': True, 'estimulados': array([19, 24, 25, 26, 27, 28]), 'espontaneos': array([ 0,  1,  2,  3,  4,  5,  6,  7,  9, 10, 11, 12, 13, 14, 15, 16, 17,
-       18, 20, 21, 22, 23]), 'jitter_limitado_por_resolucion': True, 'z': 12.125, 'p_valor': 0.004975124378109453, 'periodo_grilla_s': 10.0728, 'periodo_s': 10.09118, 'periodo_err_s': 0.00232, 'frecuencia_Hz': 0.0991, 'frecuencia_err_Hz': 2.3e-05, 'jitter_s': np.float64(0.00971), 'tolerancia_s': 0.1009, 'n_estimulados': 6, 'n_ranuras': 6, 'tasa_captura_pct': 100.0, 'tren_inicio_s': 14.8, 'tren_fin_s': 65.256, 'estimulados_dudosos': array([8]), 'n_estimulados_dudosos': 1, 'dudosos':    indice_evento  tiempo_s  ranura  desvio_s
-0              8     4.945       0    0.2355, 'resumen_grupos':                  grupo   n  ...  amplitud_mediana_px  amplitud_IQR_px
-0          estimulados   6  ...               6.8075           0.2731
-1  estimulados_dudosos   1  ...               2.0798           0.0000
-2          espontaneos  22  ...               2.0557           0.2095
-[3 rows x 10 columns], 'espontaneas_instantanea':     tiempo_s  intervalo_s  frecuencia_Hz
-0      0.656       0.5718         1.7488
-1      1.228       0.5718         1.7488
-2      1.800       0.5718         1.7488
-3      2.371       0.5718         1.7488
-4      2.943       0.5718         1.7488
-5      3.515       0.5718         1.7488
-6      4.087       0.5718         1.7488
-7      4.945       1.1437         0.8744
-8      5.786       0.5382         1.8581
-9      6.357       0.6055         1.6516
-10     6.845       0.3700         2.7026
-11     7.249       0.4373         2.2868
-12     7.770       0.6055         1.6516
-13     8.611       1.0764         0.9290
-14     9.452       0.6055         1.6516
-15    10.058       0.6055         1.6516
-16    10.932       1.1437         0.8744
-17    13.320       3.6328         0.2753
-18    15.271       0.2691         3.7161
-19    15.557       0.3027         3.3032
-20    15.944       0.4709         2.1235, 'grilla':    ranura  t_esperado_s  t_medido_s  error_s  capturada
-0       1       14.8004     14.8004     -0.0       True
-1       2       24.8916     24.8916     -0.0       True
-2       3       34.9828     34.9828      0.0       True
-3       4       45.0739     45.0739     -0.0       True
-4       5       55.1651     55.1651      0.0       True
-5       6       65.2563     65.2563      0.0       True}</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>29.72892904755024</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.7813057549858513</v>
-      </c>
-      <c r="N2" t="n">
-        <v>45.43498142534992</v>
+        <v>6</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>meseta de 28 eventos en k=6..15 (5 puntos) con 0 falsos de control</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>6-15</t>
+        </is>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03363726955655011</v>
+        <v>0.5999999999999961</v>
       </c>
       <c r="P2" t="n">
-        <v>25.18373383833654</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.5648985886406231</v>
+        <v>2.095650000000006</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>{'n_eventos': 28, 'hay_estimulacion': True, 'estimulados': array([ 8, 19, 23, 24, 25, 26, 27]), 'espontaneos': array([ 0,  1,  2,  3,  4,  5,  6,  7,  9, 10, 11, 12, 13, 14, 15, 16, 17,
+       18, 20, 21, 22]), 'z': 12.418, 'p_valor': 0.004975124378109453, 'periodo_grilla_s': 9.9652, 'periodo_s': 10.00744, 'periodo_err_s': 0.00408, 'frecuencia_Hz': 0.09993, 'frecuencia_err_Hz': 4.1e-05, 'jitter_s': 0.02092, 'tolerancia_s': 0.0667, 'n_estimulados': 7, 'n_ranuras': 7, 'tasa_captura_pct': 100.0, 'tren_inicio_s': 4.872, 'tren_fin_s': 64.94, 'estimulados_dudosos': array([], dtype=int64), 'resumen_grupos':          grupo   n  ...  amplitud_mediana_px  amplitud_IQR_px
+0  estimulados   7  ...               6.7448            0.288
+1  espontaneos  21  ...               2.0719            0.177
+[2 rows x 10 columns], 'espontaneas_instantanea':     tiempo_s  intervalo_s  frecuencia_Hz
+0      0.624       0.5717         1.7493
+1      1.191       0.5617         1.7804
+2      1.755       0.5667         1.7647
+3      2.322       0.5667         1.7647
+4      2.888       0.5667         1.7647
+5      3.454       0.5650         1.7699
+6      4.021       0.5683         1.7595
+7      4.876       1.1417         0.8759
+8      5.709       0.5250         1.9048
+9      6.272       0.6000         1.6667
+10     6.926       0.7083         1.4118
+11     7.476       0.3917         2.5532
+12     7.978       0.6117         1.6349
+13     8.811       1.0550         0.9479
+14     9.638       0.6000         1.6667
+15    10.238       0.6000         1.6667
+16    11.105       1.1333         0.8824
+17    13.611       3.8783         0.2578
+18    15.694       0.2883         3.4682
+19    16.072       0.4667         2.1429, 'grilla':    ranura  t_esperado_s  t_medido_s  error_s  capturada
+0       1        4.9067      4.8717 -0.03506       True
+1       2       14.9142     14.9383  0.02417       True
+2       3       24.9216     24.9367  0.01506       True
+3       4       34.9290     34.9367  0.00762       True
+4       5       44.9365     44.9433  0.00685       True
+5       6       54.9439     54.9367 -0.00726       True
+6       7       64.9514     64.9400 -0.01137       True}</t>
+        </is>
       </c>
       <c r="R2" t="n">
-        <v>56.89845168953592</v>
+        <v>30.00000000000171</v>
       </c>
       <c r="S2" t="n">
-        <v>18.20830783748039</v>
+        <v>0.7941614027698711</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1413888260374405</v>
+        <v>44.96406460681612</v>
       </c>
       <c r="U2" t="n">
-        <v>8.222131532717908</v>
+        <v>0.03333333333333144</v>
+      </c>
+      <c r="V2" t="n">
+        <v>25.12532911825709</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.576532305971647</v>
+      </c>
+      <c r="X2" t="n">
+        <v>56.53808084662369</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>18.24007548632138</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.146917829748726</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>8.318237030500955</v>
       </c>
     </row>
   </sheetData>
@@ -802,56 +840,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_inicio_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_fin_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>intervalo_IQR_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>frecuencia_mediana_Hz</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>CV_intervalo_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>amplitud_mediana_px</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>amplitud_IQR_px</t>
         </is>
@@ -864,91 +902,65 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>14.8</v>
+        <v>4.87</v>
       </c>
       <c r="D2" t="n">
-        <v>65.26000000000001</v>
+        <v>64.94</v>
       </c>
       <c r="E2" t="n">
-        <v>10.0912</v>
+        <v>10.0017</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.0071</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I2" t="n">
-        <v>6.8075</v>
+        <v>6.7448</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2731</v>
+        <v>0.288</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>estimulados_dudosos</t>
+          <t>espontaneos</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>4.94</v>
+        <v>0.34</v>
       </c>
       <c r="D3" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+        <v>16.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0717</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.7544</v>
+      </c>
+      <c r="H3" t="n">
+        <v>92.59999999999999</v>
+      </c>
       <c r="I3" t="n">
-        <v>2.0798</v>
+        <v>2.0719</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>22</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="D4" t="n">
-        <v>16.18</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.5718</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.0673</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.7488</v>
-      </c>
-      <c r="H4" t="n">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.0557</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.2095</v>
+        <v>0.177</v>
       </c>
     </row>
   </sheetData>
@@ -962,31 +974,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ranura</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>t_esperado_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_medido_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>error_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>capturada</t>
         </is>
@@ -997,13 +1009,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>14.8004</v>
+        <v>4.9067</v>
       </c>
       <c r="C2" t="n">
-        <v>14.8004</v>
+        <v>4.8717</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>-0.03506</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -1014,13 +1026,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>24.8916</v>
+        <v>14.9142</v>
       </c>
       <c r="C3" t="n">
-        <v>24.8916</v>
+        <v>14.9383</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0.02417</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -1031,13 +1043,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>34.9828</v>
+        <v>24.9216</v>
       </c>
       <c r="C4" t="n">
-        <v>34.9828</v>
+        <v>24.9367</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.01506</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -1048,13 +1060,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>45.0739</v>
+        <v>34.929</v>
       </c>
       <c r="C5" t="n">
-        <v>45.0739</v>
+        <v>34.9367</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>0.00762</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -1065,13 +1077,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>55.1651</v>
+        <v>44.9365</v>
       </c>
       <c r="C6" t="n">
-        <v>55.1651</v>
+        <v>44.9433</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.00685</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -1082,15 +1094,32 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>65.2563</v>
+        <v>54.9439</v>
       </c>
       <c r="C7" t="n">
-        <v>65.2563</v>
+        <v>54.9367</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.00726</v>
       </c>
       <c r="E7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>64.95140000000001</v>
+      </c>
+      <c r="C8" t="n">
+        <v>64.94</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.01137</v>
+      </c>
+      <c r="E8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1105,21 +1134,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>intervalo_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>frecuencia_Hz</t>
         </is>
@@ -1127,233 +1156,222 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.656</v>
+        <v>0.624</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5718</v>
+        <v>0.5717</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7488</v>
+        <v>1.7493</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1.228</v>
+        <v>1.191</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5718</v>
+        <v>0.5617</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7488</v>
+        <v>1.7804</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1.8</v>
+        <v>1.755</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5718</v>
+        <v>0.5667</v>
       </c>
       <c r="C4" t="n">
-        <v>1.7488</v>
+        <v>1.7647</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2.371</v>
+        <v>2.322</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5718</v>
+        <v>0.5667</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7488</v>
+        <v>1.7647</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2.943</v>
+        <v>2.888</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5718</v>
+        <v>0.5667</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7488</v>
+        <v>1.7647</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3.515</v>
+        <v>3.454</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5718</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7488</v>
+        <v>1.7699</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4.087</v>
+        <v>4.021</v>
       </c>
       <c r="B8" t="n">
-        <v>0.5718</v>
+        <v>0.5683</v>
       </c>
       <c r="C8" t="n">
-        <v>1.7488</v>
+        <v>1.7595</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4.945</v>
+        <v>4.876</v>
       </c>
       <c r="B9" t="n">
-        <v>1.1437</v>
+        <v>1.1417</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8744</v>
+        <v>0.8759</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5.786</v>
+        <v>5.709</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5382</v>
+        <v>0.525</v>
       </c>
       <c r="C10" t="n">
-        <v>1.8581</v>
+        <v>1.9048</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6.357</v>
+        <v>6.272</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6055</v>
+        <v>0.6</v>
       </c>
       <c r="C11" t="n">
-        <v>1.6516</v>
+        <v>1.6667</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6.845</v>
+        <v>6.926</v>
       </c>
       <c r="B12" t="n">
-        <v>0.37</v>
+        <v>0.7083</v>
       </c>
       <c r="C12" t="n">
-        <v>2.7026</v>
+        <v>1.4118</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7.249</v>
+        <v>7.476</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4373</v>
+        <v>0.3917</v>
       </c>
       <c r="C13" t="n">
-        <v>2.2868</v>
+        <v>2.5532</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>7.77</v>
+        <v>7.978</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6055</v>
+        <v>0.6117</v>
       </c>
       <c r="C14" t="n">
-        <v>1.6516</v>
+        <v>1.6349</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>8.611000000000001</v>
+        <v>8.811</v>
       </c>
       <c r="B15" t="n">
-        <v>1.0764</v>
+        <v>1.055</v>
       </c>
       <c r="C15" t="n">
-        <v>0.929</v>
+        <v>0.9479</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>9.452</v>
+        <v>9.638</v>
       </c>
       <c r="B16" t="n">
-        <v>0.6055</v>
+        <v>0.6</v>
       </c>
       <c r="C16" t="n">
-        <v>1.6516</v>
+        <v>1.6667</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10.058</v>
+        <v>10.238</v>
       </c>
       <c r="B17" t="n">
-        <v>0.6055</v>
+        <v>0.6</v>
       </c>
       <c r="C17" t="n">
-        <v>1.6516</v>
+        <v>1.6667</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>10.932</v>
+        <v>11.105</v>
       </c>
       <c r="B18" t="n">
-        <v>1.1437</v>
+        <v>1.1333</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8744</v>
+        <v>0.8824</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>13.32</v>
+        <v>13.611</v>
       </c>
       <c r="B19" t="n">
-        <v>3.6328</v>
+        <v>3.8783</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2753</v>
+        <v>0.2578</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>15.271</v>
+        <v>15.694</v>
       </c>
       <c r="B20" t="n">
-        <v>0.2691</v>
+        <v>0.2883</v>
       </c>
       <c r="C20" t="n">
-        <v>3.7161</v>
+        <v>3.4682</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>15.557</v>
+        <v>16.072</v>
       </c>
       <c r="B21" t="n">
-        <v>0.3027</v>
+        <v>0.4667</v>
       </c>
       <c r="C21" t="n">
-        <v>3.3032</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>15.944</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0.4709</v>
-      </c>
-      <c r="C22" t="n">
-        <v>2.1235</v>
+        <v>2.1429</v>
       </c>
     </row>
   </sheetData>
@@ -1371,37 +1389,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>amplitud_mediana_px</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>frecuencia_Hz</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>t_inicio_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>t_fin_s</t>
         </is>
@@ -1414,22 +1432,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
-        <v>2.068399999999997</v>
+        <v>2.076525000000004</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5718335824613852</v>
+        <v>0.5683333333333338</v>
       </c>
       <c r="E2" t="n">
-        <v>1.748760532208736</v>
+        <v>1.759530791788855</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3700099651220727</v>
+        <v>0.3383333333333334</v>
       </c>
       <c r="G2" t="n">
-        <v>16.17952665670154</v>
+        <v>16.305</v>
       </c>
     </row>
     <row r="3">
@@ -1445,16 +1463,16 @@
         <v>6.807450000000017</v>
       </c>
       <c r="D3" t="n">
-        <v>10.09118086696562</v>
+        <v>9.999999999999996</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09909643015849504</v>
+        <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>14.80039860488291</v>
+        <v>14.93833333333333</v>
       </c>
       <c r="G3" t="n">
-        <v>65.25630293971101</v>
+        <v>64.94</v>
       </c>
     </row>
   </sheetData>
@@ -1468,21 +1486,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
@@ -1493,10 +1511,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3700099651220727</v>
+        <v>0.3383333333333334</v>
       </c>
       <c r="C2" t="n">
-        <v>2.068399999999997</v>
+        <v>2.07185000000004</v>
       </c>
     </row>
     <row r="3">
@@ -1504,10 +1522,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9418435475834579</v>
+        <v>0.91</v>
       </c>
       <c r="C3" t="n">
-        <v>1.90564999999998</v>
+        <v>1.911099999999976</v>
       </c>
     </row>
     <row r="4">
@@ -1515,7 +1533,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1.513677130044843</v>
+        <v>1.471666666666667</v>
       </c>
       <c r="C4" t="n">
         <v>2.083199999999977</v>
@@ -1526,10 +1544,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2.085510712506228</v>
+        <v>2.038333333333334</v>
       </c>
       <c r="C5" t="n">
-        <v>2.519200000000012</v>
+        <v>2.518399999999986</v>
       </c>
     </row>
     <row r="6">
@@ -1537,7 +1555,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2.657344294967613</v>
+        <v>2.605</v>
       </c>
       <c r="C6" t="n">
         <v>2.356300000000033</v>
@@ -1548,10 +1566,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3.229177877428998</v>
+        <v>3.171666666666667</v>
       </c>
       <c r="C7" t="n">
-        <v>1.911900000000003</v>
+        <v>1.922900000000027</v>
       </c>
     </row>
     <row r="8">
@@ -1559,7 +1577,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>3.801011459890383</v>
+        <v>3.736666666666667</v>
       </c>
       <c r="C8" t="n">
         <v>2.043000000000006</v>
@@ -1570,10 +1588,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>4.372845042351769</v>
+        <v>4.305000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>1.935699999999997</v>
+        <v>1.953499999999963</v>
       </c>
     </row>
     <row r="10">
@@ -1581,10 +1599,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>4.944678624813154</v>
+        <v>4.871666666666667</v>
       </c>
       <c r="C10" t="n">
-        <v>2.079800000000034</v>
+        <v>2.0976</v>
       </c>
     </row>
     <row r="11">
@@ -1592,10 +1610,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>5.516512207274539</v>
+        <v>5.446666666666667</v>
       </c>
       <c r="C11" t="n">
-        <v>2.0899</v>
+        <v>2.093700000000013</v>
       </c>
     </row>
     <row r="12">
@@ -1603,7 +1621,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>6.054708520179372</v>
+        <v>5.971666666666667</v>
       </c>
       <c r="C12" t="n">
         <v>2.081199999999967</v>
@@ -1614,10 +1632,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>6.66017937219731</v>
+        <v>6.571666666666667</v>
       </c>
       <c r="C13" t="n">
-        <v>2.3827</v>
+        <v>2.378100000000018</v>
       </c>
     </row>
     <row r="14">
@@ -1625,10 +1643,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>7.030189337319382</v>
+        <v>7.28</v>
       </c>
       <c r="C14" t="n">
-        <v>2.123699999999985</v>
+        <v>2.12360000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1636,10 +1654,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>7.467473841554559</v>
+        <v>7.671666666666667</v>
       </c>
       <c r="C15" t="n">
-        <v>2.038400000000024</v>
+        <v>2.038999999999987</v>
       </c>
     </row>
     <row r="16">
@@ -1647,10 +1665,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>8.072944693572497</v>
+        <v>8.283333333333333</v>
       </c>
       <c r="C16" t="n">
-        <v>2.128600000000006</v>
+        <v>2.130499999999984</v>
       </c>
     </row>
     <row r="17">
@@ -1658,7 +1676,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>9.149337319382163</v>
+        <v>9.338333333333335</v>
       </c>
       <c r="C17" t="n">
         <v>2.008200000000045</v>
@@ -1669,10 +1687,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>9.7548081714001</v>
+        <v>9.938333333333334</v>
       </c>
       <c r="C18" t="n">
-        <v>2.20010000000002</v>
+        <v>2.204099999999983</v>
       </c>
     </row>
     <row r="19">
@@ -1680,7 +1698,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>10.36027902341804</v>
+        <v>10.53833333333333</v>
       </c>
       <c r="C19" t="n">
         <v>2.337699999999984</v>
@@ -1691,10 +1709,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>11.50394618834081</v>
+        <v>11.67166666666667</v>
       </c>
       <c r="C20" t="n">
-        <v>2.009899999999959</v>
+        <v>2.003600000000006</v>
       </c>
     </row>
     <row r="21">
@@ -1702,7 +1720,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>14.80039860488291</v>
+        <v>14.93833333333333</v>
       </c>
       <c r="C21" t="n">
         <v>6.993899999999996</v>
@@ -1713,10 +1731,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>15.13677130044843</v>
+        <v>15.55</v>
       </c>
       <c r="C22" t="n">
-        <v>1.662700000000029</v>
+        <v>1.886000000000024</v>
       </c>
     </row>
     <row r="23">
@@ -1724,10 +1742,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>15.40586945690085</v>
+        <v>15.83833333333333</v>
       </c>
       <c r="C23" t="n">
-        <v>1.870900000000006</v>
+        <v>1.691100000000006</v>
       </c>
     </row>
     <row r="24">
@@ -1735,10 +1753,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>15.70860488290982</v>
+        <v>16.305</v>
       </c>
       <c r="C24" t="n">
-        <v>1.676699999999983</v>
+        <v>1.300000000000011</v>
       </c>
     </row>
     <row r="25">
@@ -1746,10 +1764,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>16.17952665670154</v>
+        <v>24.93666666666667</v>
       </c>
       <c r="C25" t="n">
-        <v>1.300000000000011</v>
+        <v>7.032300000000021</v>
       </c>
     </row>
     <row r="26">
@@ -1757,10 +1775,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>24.89157947184853</v>
+        <v>34.93666666666667</v>
       </c>
       <c r="C26" t="n">
-        <v>7.032300000000021</v>
+        <v>6.870100000000036</v>
       </c>
     </row>
     <row r="27">
@@ -1768,10 +1786,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>34.98276033881415</v>
+        <v>44.94333333333334</v>
       </c>
       <c r="C27" t="n">
-        <v>6.870100000000036</v>
+        <v>6.675000000000011</v>
       </c>
     </row>
     <row r="28">
@@ -1779,10 +1797,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>45.07394120577977</v>
+        <v>54.93666666666667</v>
       </c>
       <c r="C28" t="n">
-        <v>6.67149999999998</v>
+        <v>6.613</v>
       </c>
     </row>
     <row r="29">
@@ -1790,20 +1808,9 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>55.16512207274539</v>
+        <v>64.94</v>
       </c>
       <c r="C29" t="n">
-        <v>6.613</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="n">
-        <v>65.25630293971101</v>
-      </c>
-      <c r="C30" t="n">
         <v>6.744799999999998</v>
       </c>
     </row>

--- a/data/processed_data/Video_prueba/contracciones.xlsx
+++ b/data/processed_data/Video_prueba/contracciones.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="espont_Video_prueba" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="poblac_Video_prueba" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eventos_Video_prueba" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cinetica_Video_prueba" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -567,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AS2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,6 +705,96 @@
       <c r="AA1" t="inlineStr">
         <is>
           <t>blur_sigma</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>cinetica_min_frames</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_iqr_pct</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>ttp_n_eventos</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>ttp_frames_mediana</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>ttp_reportable</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>ttp_iqr_s</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>ttp_cota_inf_s</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>ttp_cota_sup_s</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>rt50_n_eventos</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>rt50_frames_mediana</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>rt50_reportable</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>rt50_iqr_s</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>rt50_cota_inf_s</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>rt50_cota_sup_s</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>cinetica_motivo</t>
         </is>
       </c>
     </row>
@@ -828,6 +919,56 @@
       <c r="AA2" t="n">
         <v>8.318237030500955</v>
       </c>
+      <c r="AB2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.7123415093264255</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.6822-0.8202</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.1016666666666666</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.1025000000000009</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>TTP: 2 fotogramas (&lt; 5); solo cota TTP &lt; 102 ms; RT50: 2 fotogramas (&lt; 5); solo cota RT50 &lt; 103 ms</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1817,4 +1958,2090 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>evento</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>grupo</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>frame_pico</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tiempo_s</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>grosor_reposo_px</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>meseta_pico_frames</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>onset_s</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ttp_frames</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ttp_min_s</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ttp_max_s</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ttp_medible</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>rt50_frames</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>rt50_min_s</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>rt50_max_s</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>rt50_medible</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>offset_s</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>duracion_frames</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>duracion_s</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3383333333333334</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.07185000000004</v>
+      </c>
+      <c r="F2" t="n">
+        <v>294.1864426311154</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7042642691043255</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.277989655707567</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.06034367762576642</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.09833333333333333</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.04847599810750691</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.4330979839398581</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.1551083282322911</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.911099999999976</v>
+      </c>
+      <c r="F3" t="n">
+        <v>294.1858218643109</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6496234209687523</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8592479658844149</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.05075203411558515</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.06212855624788582</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.1416666666666663</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.032840827980012</v>
+      </c>
+      <c r="U3" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.1735928620955974</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>45</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.471666666666667</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.083199999999977</v>
+      </c>
+      <c r="F4" t="n">
+        <v>294.2004470505327</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7080886589006985</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.41853570329332</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.05313096337334677</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1083333333333329</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.07726777939042195</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.02500000000000013</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.133333333333334</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.598569790012352</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.180034086719032</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>62</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.038333333333334</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.518399999999986</v>
+      </c>
+      <c r="F5" t="n">
+        <v>294.2096897179222</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8559881227618772</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.982052650145516</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.05628068318781798</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1000000000000003</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.05580770747092556</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.09333333333333282</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.14553618388036</v>
+      </c>
+      <c r="U5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.1634835337348437</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.356300000000033</v>
+      </c>
+      <c r="F6" t="n">
+        <v>294.2180072554883</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8008687238350802</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.553522137404581</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.05147786259541931</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.09833333333333316</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.06237304750793804</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.1000000000000001</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.708330000000001</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.1548078625954203</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>96</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.171666666666667</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.922900000000027</v>
+      </c>
+      <c r="F7" t="n">
+        <v>294.2257620822632</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6535457624075758</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.127293428757324</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.04437323790934311</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1333333333333342</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0682990182060812</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.1333333333333329</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.281085168239442</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.1537917394821178</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>113</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.736666666666667</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.043000000000006</v>
+      </c>
+      <c r="F8" t="n">
+        <v>294.1927371840952</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6944427043151546</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.688532583577262</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.04813408308940481</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.07283428968874883</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.1083333333333329</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.845477477477479</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.1569448939002172</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>130</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.305000000000001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.953499999999963</v>
+      </c>
+      <c r="F9" t="n">
+        <v>294.1927371840952</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6640204713067178</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.253494974191794</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.05150502580820682</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.1333333333333337</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.07340231680333265</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.1333333333333329</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4.418203921568629</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.1647089473768348</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>147</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.871666666666667</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.0976</v>
+      </c>
+      <c r="F10" t="n">
+        <v>294.1914281912706</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7130051384897016</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.817098754578756</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.05456791208791145</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.09833333333333272</v>
+      </c>
+      <c r="N10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.06285318951238228</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.1016666666666657</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4.980667027221918</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.163568272643162</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>164</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.446666666666667</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.093700000000013</v>
+      </c>
+      <c r="F11" t="n">
+        <v>294.1920858240023</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7116778801631494</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.378556092306326</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0681105743603414</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.1016666666666666</v>
+      </c>
+      <c r="N11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.05135885071328072</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.1133333333333333</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5.586102227298683</v>
+      </c>
+      <c r="U11" t="n">
+        <v>7</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.2075461349923575</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>180</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.971666666666667</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.081199999999967</v>
+      </c>
+      <c r="F12" t="n">
+        <v>294.1757204680609</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7074683106711134</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5.91788425690561</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.05378240976105708</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1083333333333334</v>
+      </c>
+      <c r="N12" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.07456235663406829</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.02500000000000036</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.1333333333333346</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6.099438589379813</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.1815543324742031</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>198</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6.571666666666667</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.378100000000018</v>
+      </c>
+      <c r="F13" t="n">
+        <v>294.2090886717923</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8083026974917588</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6.508522902232486</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.06314376443418102</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.03000000000000025</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.1333333333333337</v>
+      </c>
+      <c r="N13" t="b">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.04022487482117132</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.1033333333333335</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>6.664180808080808</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.1556579058483214</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>209</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.12360000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>294.1229333192736</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.7220110230897295</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>7.265851470196322</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.01414852980367787</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.03333333333333321</v>
+      </c>
+      <c r="N14" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.008140141061024231</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.03333333333333321</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7.294652253909844</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.02880078371352202</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>222</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7.671666666666667</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.038999999999987</v>
+      </c>
+      <c r="F15" t="n">
+        <v>294.1707185111845</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.6931349286970123</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7.610206812652068</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.06145985401459875</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="N15" t="b">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.06134544667964548</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.1000000000000005</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>7.780480532638585</v>
+      </c>
+      <c r="U15" t="n">
+        <v>6</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.1702737199865165</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>240</v>
+      </c>
+      <c r="D16" t="n">
+        <v>8.283333333333333</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.130499999999984</v>
+      </c>
+      <c r="F16" t="n">
+        <v>294.2228176658223</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7241110723165602</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8.206060895395717</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.07727243793761573</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.02333333333333165</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.1316666666666677</v>
+      </c>
+      <c r="N16" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.03071177337325892</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.1016666666666683</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>8.359612132624427</v>
+      </c>
+      <c r="U16" t="n">
+        <v>6</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.1535512372287098</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>272</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9.338333333333335</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.008200000000045</v>
+      </c>
+      <c r="F17" t="n">
+        <v>294.1947370693252</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.6826090840390611</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>9.283307124765994</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.05502620856734097</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="N17" t="b">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.06638977509945043</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.1033333333333335</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>9.454144519370622</v>
+      </c>
+      <c r="U17" t="n">
+        <v>6</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.1708373946046287</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>290</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9.938333333333334</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.204099999999983</v>
+      </c>
+      <c r="F18" t="n">
+        <v>294.2034913291759</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.7491753378051785</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>9.884551580034749</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.05378175329858514</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="N18" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.0773669686169729</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.0400000000000027</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.1316666666666695</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>10.07473637722517</v>
+      </c>
+      <c r="U18" t="n">
+        <v>7</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.1901847971904207</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>308</v>
+      </c>
+      <c r="D19" t="n">
+        <v>10.53833333333333</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.337699999999984</v>
+      </c>
+      <c r="F19" t="n">
+        <v>294.214226572169</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.7945570910135985</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>10.46726430976431</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.07106902356901834</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.04000000000000092</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.13333333333334</v>
+      </c>
+      <c r="N19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.04524162297698275</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.09333333333333016</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>10.63149036402569</v>
+      </c>
+      <c r="U19" t="n">
+        <v>6</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.1642260542613805</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>342</v>
+      </c>
+      <c r="D20" t="n">
+        <v>11.67166666666667</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.003600000000006</v>
+      </c>
+      <c r="F20" t="n">
+        <v>294.2496961314328</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6809182902622457</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>11.60524413625615</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.06642253041052015</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="N20" t="b">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.04391438782475277</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>11.77693206064009</v>
+      </c>
+      <c r="U20" t="n">
+        <v>6</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.1716879243839351</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>440</v>
+      </c>
+      <c r="D21" t="n">
+        <v>14.93833333333333</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6.993899999999996</v>
+      </c>
+      <c r="F21" t="n">
+        <v>294.2013271098332</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.377249643537124</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>14.87483939589281</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.06349393744052101</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="N21" t="b">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.06385769271328279</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.1066666666666709</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>15.06080248463021</v>
+      </c>
+      <c r="U21" t="n">
+        <v>6</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.1859630887374042</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>458</v>
+      </c>
+      <c r="D22" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.886000000000024</v>
+      </c>
+      <c r="F22" t="n">
+        <v>294.1186033098035</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.6412379151730999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>15.47975843239103</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.07024156760896716</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="N22" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.03859905521109752</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.09333333333333016</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>15.62125419354839</v>
+      </c>
+      <c r="U22" t="n">
+        <v>5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.1414957611573548</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>467</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15.83833333333333</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.691100000000006</v>
+      </c>
+      <c r="F23" t="n">
+        <v>294.1159046764791</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.5749774062236376</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>15.76352863317127</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.07480470016206375</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.1333333333333293</v>
+      </c>
+      <c r="N23" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.04981108035675774</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.1316666666666588</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>15.94463069544365</v>
+      </c>
+      <c r="U23" t="n">
+        <v>7</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.1811020622723802</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>481</v>
+      </c>
+      <c r="D24" t="n">
+        <v>16.305</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.300000000000011</v>
+      </c>
+      <c r="F24" t="n">
+        <v>294.1511484325545</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.4419496598695369</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>16.24686112692089</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.05813887307911259</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.13333333333334</v>
+      </c>
+      <c r="N24" t="b">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.07519988155167567</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.1316666666666713</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>16.45064314590225</v>
+      </c>
+      <c r="U24" t="n">
+        <v>7</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.2037820189813608</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>740</v>
+      </c>
+      <c r="D25" t="n">
+        <v>24.93666666666667</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7.032300000000021</v>
+      </c>
+      <c r="F25" t="n">
+        <v>294.2397232959303</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.389990012642622</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>24.87587979664488</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.06078687002178995</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.1016666666666701</v>
+      </c>
+      <c r="N25" t="b">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.05946369636963311</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.09833333333332916</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>25.06408252781716</v>
+      </c>
+      <c r="U25" t="n">
+        <v>6</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.1882027311722823</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D26" t="n">
+        <v>34.93666666666667</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6.870100000000036</v>
+      </c>
+      <c r="F26" t="n">
+        <v>294.191975712738</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.335243843193162</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>34.87568189346437</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.06098477320229989</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.09833333333332916</v>
+      </c>
+      <c r="N26" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.06340293333334301</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.1033333333333388</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>35.0598166372722</v>
+      </c>
+      <c r="U26" t="n">
+        <v>6</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.1841347438078316</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1340</v>
+      </c>
+      <c r="D27" t="n">
+        <v>44.94333333333334</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6.675000000000011</v>
+      </c>
+      <c r="F27" t="n">
+        <v>294.1677991825377</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.269113077144798</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>44.87580165150298</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.06753168183035996</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.1049999999999969</v>
+      </c>
+      <c r="N27" t="b">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.05389935763220421</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.09833333333333627</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>45.06119392119393</v>
+      </c>
+      <c r="U27" t="n">
+        <v>6</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.1853922696909436</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1640</v>
+      </c>
+      <c r="D28" t="n">
+        <v>54.93666666666667</v>
+      </c>
+      <c r="E28" t="n">
+        <v>6.613</v>
+      </c>
+      <c r="F28" t="n">
+        <v>294.1908725605803</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.247860357611278</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>54.87984217671682</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.05682448994984668</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.1016666666666666</v>
+      </c>
+      <c r="N28" t="b">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.06207670532109688</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>55.06085729759004</v>
+      </c>
+      <c r="U28" t="n">
+        <v>6</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.1810151208732194</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1940</v>
+      </c>
+      <c r="D29" t="n">
+        <v>64.94</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6.744799999999998</v>
+      </c>
+      <c r="F29" t="n">
+        <v>294.1102572478565</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.293289619721059</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>64.87544567409766</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.06455432590233556</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.09833333333332916</v>
+      </c>
+      <c r="N29" t="b">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.05568519369163027</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.1016666666666595</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>65.05270866845399</v>
+      </c>
+      <c r="U29" t="n">
+        <v>6</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.177262994356326</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/processed_data/Video_prueba/contracciones.xlsx
+++ b/data/processed_data/Video_prueba/contracciones.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
         <v>0.2562</v>
       </c>
       <c r="C2" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -461,13 +461,13 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3416</v>
+        <v>0.2818</v>
       </c>
       <c r="C3" t="n">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -475,13 +475,13 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>3.63</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5124</v>
+        <v>0.31</v>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -489,13 +489,13 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
+        <v>3.993</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6832</v>
+        <v>0.341</v>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -503,13 +503,13 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>10</v>
+        <v>4.392</v>
       </c>
       <c r="B6" t="n">
-        <v>0.854</v>
+        <v>0.3751</v>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -517,13 +517,13 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>12</v>
+        <v>4.832</v>
       </c>
       <c r="B7" t="n">
-        <v>1.0248</v>
+        <v>0.4126</v>
       </c>
       <c r="C7" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -531,13 +531,13 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>15</v>
+        <v>5.315</v>
       </c>
       <c r="B8" t="n">
-        <v>1.281</v>
+        <v>0.4539</v>
       </c>
       <c r="C8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -545,15 +545,225 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20</v>
+        <v>5.846</v>
       </c>
       <c r="B9" t="n">
-        <v>1.708</v>
+        <v>0.4992</v>
       </c>
       <c r="C9" t="n">
+        <v>29</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6.431</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.5492</v>
+      </c>
+      <c r="C10" t="n">
+        <v>29</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7.074</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.6041</v>
+      </c>
+      <c r="C11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7.781</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.6645</v>
+      </c>
+      <c r="C12" t="n">
+        <v>29</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8.558999999999999</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.7309</v>
+      </c>
+      <c r="C13" t="n">
+        <v>29</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9.414999999999999</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.804</v>
+      </c>
+      <c r="C14" t="n">
+        <v>29</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10.357</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.8845</v>
+      </c>
+      <c r="C15" t="n">
+        <v>29</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11.392</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.9729</v>
+      </c>
+      <c r="C16" t="n">
+        <v>29</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12.532</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1.0702</v>
+      </c>
+      <c r="C17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13.785</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1.1772</v>
+      </c>
+      <c r="C18" t="n">
+        <v>29</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>15.163</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1.2949</v>
+      </c>
+      <c r="C19" t="n">
+        <v>29</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1.4244</v>
+      </c>
+      <c r="C20" t="n">
+        <v>28</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>18.348</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1.5669</v>
+      </c>
+      <c r="C21" t="n">
+        <v>28</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20.182</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1.7235</v>
+      </c>
+      <c r="C22" t="n">
         <v>26</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22.201</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1.8959</v>
+      </c>
+      <c r="C23" t="n">
+        <v>25</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>24.421</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2.0855</v>
+      </c>
+      <c r="C24" t="n">
+        <v>15</v>
+      </c>
+      <c r="D24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -568,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS2"/>
+  <dimension ref="A1:BD2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +1007,61 @@
           <t>cinetica_motivo</t>
         </is>
       </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>fotogramas_sin_medida</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>fotogramas_sin_medida_pct</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>fotogramas_low_quality</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>eventos_junto_a_hueco</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>win_s_usado</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>win_s_automatico</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>duracion_evento_max_s</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>ventana_corta</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>conteo_por_ventana</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>conteo_estable_ventana</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>mesetas</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -823,10 +1088,10 @@
         <v>0.09005957368569244</v>
       </c>
       <c r="H2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>9.414999999999999</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -836,29 +1101,29 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>meseta de 28 eventos en k=6..15 (5 puntos) con 0 falsos de control</t>
+          <t>meseta de 29 eventos en k=5.315..15.163 (x2.85) con 0 falsos de control</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>6-15</t>
+          <t>5.315-15.163</t>
         </is>
       </c>
       <c r="N2" t="b">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5999999999999961</v>
+        <v>0.5733333333333335</v>
       </c>
       <c r="P2" t="n">
-        <v>2.095650000000006</v>
+        <v>2.093700000000013</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'n_eventos': 28, 'hay_estimulacion': True, 'estimulados': array([ 8, 19, 23, 24, 25, 26, 27]), 'espontaneos': array([ 0,  1,  2,  3,  4,  5,  6,  7,  9, 10, 11, 12, 13, 14, 15, 16, 17,
-       18, 20, 21, 22]), 'z': 12.418, 'p_valor': 0.004975124378109453, 'periodo_grilla_s': 9.9652, 'periodo_s': 10.00744, 'periodo_err_s': 0.00408, 'frecuencia_Hz': 0.09993, 'frecuencia_err_Hz': 4.1e-05, 'jitter_s': 0.02092, 'tolerancia_s': 0.0667, 'n_estimulados': 7, 'n_ranuras': 7, 'tasa_captura_pct': 100.0, 'tren_inicio_s': 4.872, 'tren_fin_s': 64.94, 'estimulados_dudosos': array([], dtype=int64), 'resumen_grupos':          grupo   n  ...  amplitud_mediana_px  amplitud_IQR_px
-0  estimulados   7  ...               6.7448            0.288
-1  espontaneos  21  ...               2.0719            0.177
+          <t>{'n_eventos': 29, 'hay_estimulacion': True, 'estimulados': array([ 8, 19, 24, 25, 26, 27, 28]), 'espontaneos': array([ 0,  1,  2,  3,  4,  5,  6,  7,  9, 10, 11, 12, 13, 14, 15, 16, 17,
+       18, 20, 21, 22, 23]), 'z': 12.112, 'p_valor': 0.004975124378109453, 'periodo_grilla_s': 9.9652, 'periodo_s': 10.00744, 'periodo_err_s': 0.00408, 'frecuencia_Hz': 0.09993, 'frecuencia_err_Hz': 4.1e-05, 'jitter_s': 0.02092, 'tolerancia_s': 0.0667, 'n_estimulados': 7, 'n_ranuras': 7, 'tasa_captura_pct': 100.0, 'tren_inicio_s': 4.872, 'tren_fin_s': 64.94, 'estimulados_dudosos': array([], dtype=int64), 'resumen_grupos':          grupo   n  ...  amplitud_mediana_px  amplitud_IQR_px
+0  estimulados   7  ...               6.7448           0.2880
+1  espontaneos  22  ...               2.0574           0.1982
 [2 rows x 10 columns], 'espontaneas_instantanea':     tiempo_s  intervalo_s  frecuencia_Hz
 0      0.624       0.5717         1.7493
 1      1.191       0.5617         1.7804
@@ -877,9 +1142,10 @@
 14     9.638       0.6000         1.6667
 15    10.238       0.6000         1.6667
 16    11.105       1.1333         0.8824
-17    13.611       3.8783         0.2578
-18    15.694       0.2883         3.4682
-19    16.072       0.4667         2.1429, 'grilla':    ranura  t_esperado_s  t_medido_s  error_s  capturada
+17    13.475       3.6067         0.2773
+18    15.414       0.2717         3.6810
+19    15.694       0.2883         3.4682
+20    16.072       0.4667         2.1429, 'grilla':    ranura  t_esperado_s  t_medido_s  error_s  capturada
 0       1        4.9067      4.8717 -0.03506       True
 1       2       14.9142     14.9383  0.02417       True
 2       3       24.9216     24.9367  0.01506       True
@@ -893,45 +1159,45 @@
         <v>30.00000000000171</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7941614027698711</v>
+        <v>0.7791516860101292</v>
       </c>
       <c r="T2" t="n">
-        <v>44.96406460681612</v>
+        <v>44.954586783267</v>
       </c>
       <c r="U2" t="n">
         <v>0.03333333333333144</v>
       </c>
       <c r="V2" t="n">
-        <v>25.12532911825709</v>
+        <v>25.09090808741698</v>
       </c>
       <c r="W2" t="n">
-        <v>0.576532305971647</v>
+        <v>0.5641420588386948</v>
       </c>
       <c r="X2" t="n">
-        <v>56.53808084662369</v>
+        <v>56.37688833913355</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.24007548632138</v>
+        <v>18.16698442770726</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.146917829748726</v>
+        <v>0.1423492913694502</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.318237030500955</v>
+        <v>8.213103670703363</v>
       </c>
       <c r="AB2" t="n">
         <v>5</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7123415093264255</v>
+        <v>0.7116778801631494</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.6822-0.8202</t>
+          <t>0.6809-0.8083</t>
         </is>
       </c>
       <c r="AE2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF2" t="n">
         <v>2</v>
@@ -948,7 +1214,7 @@
         <v>0.1016666666666666</v>
       </c>
       <c r="AL2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM2" t="n">
         <v>2</v>
@@ -962,11 +1228,48 @@
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.1025000000000009</v>
+        <v>0.1016666666666683</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>TTP: 2 fotogramas (&lt; 5); solo cota TTP &lt; 102 ms; RT50: 2 fotogramas (&lt; 5); solo cota RT50 &lt; 103 ms</t>
+          <t>TTP: 2 fotogramas (&lt; 5); solo cota TTP &lt; 102 ms; RT50: 2 fotogramas (&lt; 5); solo cota RT50 &lt; 102 ms</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.2333333333333201</v>
+      </c>
+      <c r="BA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>1.5 s: 29 | 2 s: 29 | 3 s: 29</t>
+        </is>
+      </c>
+      <c r="BC2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>29 ev en k=5.315-15.163</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1380,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
         <v>0.34</v>
@@ -1086,22 +1389,22 @@
         <v>16.3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.57</v>
+        <v>0.5683</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0717</v>
+        <v>0.05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7544</v>
+        <v>1.7595</v>
       </c>
       <c r="H3" t="n">
-        <v>92.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0719</v>
+        <v>2.0574</v>
       </c>
       <c r="J3" t="n">
-        <v>0.177</v>
+        <v>0.1982</v>
       </c>
     </row>
   </sheetData>
@@ -1275,7 +1578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1484,34 +1787,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>13.611</v>
+        <v>13.475</v>
       </c>
       <c r="B19" t="n">
-        <v>3.8783</v>
+        <v>3.6067</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2578</v>
+        <v>0.2773</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>15.694</v>
+        <v>15.414</v>
       </c>
       <c r="B20" t="n">
-        <v>0.2883</v>
+        <v>0.2717</v>
       </c>
       <c r="C20" t="n">
-        <v>3.4682</v>
+        <v>3.681</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>15.694</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.2883</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.4682</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
         <v>16.072</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>0.4667</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>2.1429</v>
       </c>
     </row>
@@ -1573,16 +1887,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>2.076525000000004</v>
+        <v>2.07185000000004</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5683333333333338</v>
+        <v>0.5675000000000004</v>
       </c>
       <c r="E2" t="n">
-        <v>1.759530791788855</v>
+        <v>1.762114537444933</v>
       </c>
       <c r="F2" t="n">
         <v>0.3383333333333334</v>
@@ -1627,7 +1941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1646,6 +1960,11 @@
           <t>amplitud_px</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>junto_a_hueco</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1657,6 +1976,9 @@
       <c r="C2" t="n">
         <v>2.07185000000004</v>
       </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1667,6 +1989,9 @@
       </c>
       <c r="C3" t="n">
         <v>1.911099999999976</v>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1679,6 +2004,9 @@
       <c r="C4" t="n">
         <v>2.083199999999977</v>
       </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1690,6 +2018,9 @@
       <c r="C5" t="n">
         <v>2.518399999999986</v>
       </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1701,6 +2032,9 @@
       <c r="C6" t="n">
         <v>2.356300000000033</v>
       </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1712,6 +2046,9 @@
       <c r="C7" t="n">
         <v>1.922900000000027</v>
       </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1723,6 +2060,9 @@
       <c r="C8" t="n">
         <v>2.043000000000006</v>
       </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1734,6 +2074,9 @@
       <c r="C9" t="n">
         <v>1.953499999999963</v>
       </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1745,6 +2088,9 @@
       <c r="C10" t="n">
         <v>2.0976</v>
       </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1756,6 +2102,9 @@
       <c r="C11" t="n">
         <v>2.093700000000013</v>
       </c>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1767,6 +2116,9 @@
       <c r="C12" t="n">
         <v>2.081199999999967</v>
       </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1778,6 +2130,9 @@
       <c r="C13" t="n">
         <v>2.378100000000018</v>
       </c>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1789,6 +2144,9 @@
       <c r="C14" t="n">
         <v>2.12360000000001</v>
       </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1800,6 +2158,9 @@
       <c r="C15" t="n">
         <v>2.038999999999987</v>
       </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1811,6 +2172,9 @@
       <c r="C16" t="n">
         <v>2.130499999999984</v>
       </c>
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1822,6 +2186,9 @@
       <c r="C17" t="n">
         <v>2.008200000000045</v>
       </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1833,6 +2200,9 @@
       <c r="C18" t="n">
         <v>2.204099999999983</v>
       </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1844,6 +2214,9 @@
       <c r="C19" t="n">
         <v>2.337699999999984</v>
       </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1855,6 +2228,9 @@
       <c r="C20" t="n">
         <v>2.003600000000006</v>
       </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1866,16 +2242,22 @@
       <c r="C21" t="n">
         <v>6.993899999999996</v>
       </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>15.55</v>
+        <v>15.27833333333333</v>
       </c>
       <c r="C22" t="n">
-        <v>1.886000000000024</v>
+        <v>1.662700000000029</v>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1883,10 +2265,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>15.83833333333333</v>
+        <v>15.55</v>
       </c>
       <c r="C23" t="n">
-        <v>1.691100000000006</v>
+        <v>1.886000000000024</v>
+      </c>
+      <c r="D23" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1894,10 +2279,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>16.305</v>
+        <v>15.83833333333333</v>
       </c>
       <c r="C24" t="n">
-        <v>1.300000000000011</v>
+        <v>1.691100000000006</v>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1905,10 +2293,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>24.93666666666667</v>
+        <v>16.305</v>
       </c>
       <c r="C25" t="n">
-        <v>7.032300000000021</v>
+        <v>1.300000000000011</v>
+      </c>
+      <c r="D25" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1916,10 +2307,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>34.93666666666667</v>
+        <v>24.93666666666667</v>
       </c>
       <c r="C26" t="n">
-        <v>6.870100000000036</v>
+        <v>7.032300000000021</v>
+      </c>
+      <c r="D26" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1927,10 +2321,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>44.94333333333334</v>
+        <v>34.93666666666667</v>
       </c>
       <c r="C27" t="n">
-        <v>6.675000000000011</v>
+        <v>6.870100000000036</v>
+      </c>
+      <c r="D27" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1938,10 +2335,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>54.93666666666667</v>
+        <v>44.94333333333334</v>
       </c>
       <c r="C28" t="n">
-        <v>6.613</v>
+        <v>6.675000000000011</v>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1949,10 +2349,27 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
+        <v>54.93666666666667</v>
+      </c>
+      <c r="C29" t="n">
+        <v>6.613</v>
+      </c>
+      <c r="D29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
         <v>64.94</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C30" t="n">
         <v>6.744799999999998</v>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1966,7 +2383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V29"/>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3491,37 +3908,37 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="D22" t="n">
-        <v>15.55</v>
+        <v>15.27833333333333</v>
       </c>
       <c r="E22" t="n">
-        <v>1.886000000000024</v>
+        <v>1.662700000000029</v>
       </c>
       <c r="F22" t="n">
-        <v>294.1186033098035</v>
+        <v>294.1564625285545</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6412379151730999</v>
+        <v>0.5652434033600832</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>15.47975843239103</v>
+        <v>15.21000861528822</v>
       </c>
       <c r="J22" t="n">
         <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>0.07024156760896716</v>
+        <v>0.06832471804511009</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.09999999999999964</v>
+        <v>0.09833333333332916</v>
       </c>
       <c r="N22" t="b">
         <v>0</v>
@@ -3530,25 +3947,25 @@
         <v>2</v>
       </c>
       <c r="P22" t="n">
-        <v>0.03859905521109752</v>
+        <v>0.03594812742143461</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.09333333333333016</v>
+        <v>0.1016666666666595</v>
       </c>
       <c r="S22" t="b">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>15.62125419354839</v>
+        <v>15.35982679647658</v>
       </c>
       <c r="U22" t="n">
         <v>5</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1414957611573548</v>
+        <v>0.1498181811883619</v>
       </c>
     </row>
     <row r="23">
@@ -3561,37 +3978,37 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="D23" t="n">
-        <v>15.83833333333333</v>
+        <v>15.55</v>
       </c>
       <c r="E23" t="n">
-        <v>1.691100000000006</v>
+        <v>1.886000000000024</v>
       </c>
       <c r="F23" t="n">
-        <v>294.1159046764791</v>
+        <v>294.1186033098035</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5749774062236376</v>
+        <v>0.6412379151730999</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>15.76352863317127</v>
+        <v>15.47975843239103</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>0.07480470016206375</v>
+        <v>0.07024156760896716</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1333333333333293</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="N23" t="b">
         <v>0</v>
@@ -3600,25 +4017,25 @@
         <v>2</v>
       </c>
       <c r="P23" t="n">
-        <v>0.04981108035675774</v>
+        <v>0.03859905521109752</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1316666666666588</v>
+        <v>0.09333333333333016</v>
       </c>
       <c r="S23" t="b">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>15.94463069544365</v>
+        <v>15.62125419354839</v>
       </c>
       <c r="U23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1811020622723802</v>
+        <v>0.1414957611573548</v>
       </c>
     </row>
     <row r="24">
@@ -3631,64 +4048,64 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="D24" t="n">
-        <v>16.305</v>
+        <v>15.83833333333333</v>
       </c>
       <c r="E24" t="n">
-        <v>1.300000000000011</v>
+        <v>1.691100000000006</v>
       </c>
       <c r="F24" t="n">
-        <v>294.1511484325545</v>
+        <v>294.1159046764791</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4419496598695369</v>
+        <v>0.5749774062236376</v>
       </c>
       <c r="H24" t="n">
         <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>16.24686112692089</v>
+        <v>15.76352863317127</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>0.05813887307911259</v>
+        <v>0.07480470016206375</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.13333333333334</v>
+        <v>0.1333333333333293</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P24" t="n">
-        <v>0.07519988155167567</v>
+        <v>0.04981108035675774</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1316666666666713</v>
+        <v>0.1316666666666588</v>
       </c>
       <c r="S24" t="b">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>16.45064314590225</v>
+        <v>15.94463069544365</v>
       </c>
       <c r="U24" t="n">
         <v>7</v>
       </c>
       <c r="V24" t="n">
-        <v>0.2037820189813608</v>
+        <v>0.1811020622723802</v>
       </c>
     </row>
     <row r="25">
@@ -3697,68 +4114,68 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>estimulados</t>
+          <t>espontaneos</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>740</v>
+        <v>481</v>
       </c>
       <c r="D25" t="n">
-        <v>24.93666666666667</v>
+        <v>16.305</v>
       </c>
       <c r="E25" t="n">
-        <v>7.032300000000021</v>
+        <v>1.300000000000011</v>
       </c>
       <c r="F25" t="n">
-        <v>294.2397232959303</v>
+        <v>294.1511484325545</v>
       </c>
       <c r="G25" t="n">
-        <v>2.389990012642622</v>
+        <v>0.4419496598695369</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>24.87587979664488</v>
+        <v>16.24686112692089</v>
       </c>
       <c r="J25" t="n">
         <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>0.06078687002178995</v>
+        <v>0.05813887307911259</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1016666666666701</v>
+        <v>0.13333333333334</v>
       </c>
       <c r="N25" t="b">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>0.05946369636963311</v>
+        <v>0.07519988155167567</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.09833333333332916</v>
+        <v>0.1316666666666713</v>
       </c>
       <c r="S25" t="b">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>25.06408252781716</v>
+        <v>16.45064314590225</v>
       </c>
       <c r="U25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V25" t="n">
-        <v>0.1882027311722823</v>
+        <v>0.2037820189813608</v>
       </c>
     </row>
     <row r="26">
@@ -3771,64 +4188,64 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1040</v>
+        <v>740</v>
       </c>
       <c r="D26" t="n">
-        <v>34.93666666666667</v>
+        <v>24.93666666666667</v>
       </c>
       <c r="E26" t="n">
-        <v>6.870100000000036</v>
+        <v>7.032300000000021</v>
       </c>
       <c r="F26" t="n">
-        <v>294.191975712738</v>
+        <v>294.2397232959303</v>
       </c>
       <c r="G26" t="n">
-        <v>2.335243843193162</v>
+        <v>2.389990012642622</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>34.87568189346437</v>
+        <v>24.87587979664488</v>
       </c>
       <c r="J26" t="n">
         <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.06098477320229989</v>
+        <v>0.06078687002178995</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
+        <v>0.1016666666666701</v>
+      </c>
+      <c r="N26" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.05946369636963311</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
         <v>0.09833333333332916</v>
       </c>
-      <c r="N26" t="b">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0.06340293333334301</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0.1033333333333388</v>
-      </c>
       <c r="S26" t="b">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>35.0598166372722</v>
+        <v>25.06408252781716</v>
       </c>
       <c r="U26" t="n">
         <v>6</v>
       </c>
       <c r="V26" t="n">
-        <v>0.1841347438078316</v>
+        <v>0.1882027311722823</v>
       </c>
     </row>
     <row r="27">
@@ -3841,37 +4258,37 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1340</v>
+        <v>1040</v>
       </c>
       <c r="D27" t="n">
-        <v>44.94333333333334</v>
+        <v>34.93666666666667</v>
       </c>
       <c r="E27" t="n">
-        <v>6.675000000000011</v>
+        <v>6.870100000000036</v>
       </c>
       <c r="F27" t="n">
-        <v>294.1677991825377</v>
+        <v>294.191975712738</v>
       </c>
       <c r="G27" t="n">
-        <v>2.269113077144798</v>
+        <v>2.335243843193162</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>44.87580165150298</v>
+        <v>34.87568189346437</v>
       </c>
       <c r="J27" t="n">
         <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>0.06753168183035996</v>
+        <v>0.06098477320229989</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1049999999999969</v>
+        <v>0.09833333333332916</v>
       </c>
       <c r="N27" t="b">
         <v>0</v>
@@ -3880,25 +4297,25 @@
         <v>2</v>
       </c>
       <c r="P27" t="n">
-        <v>0.05389935763220421</v>
+        <v>0.06340293333334301</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0.09833333333333627</v>
+        <v>0.1033333333333388</v>
       </c>
       <c r="S27" t="b">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>45.06119392119393</v>
+        <v>35.0598166372722</v>
       </c>
       <c r="U27" t="n">
         <v>6</v>
       </c>
       <c r="V27" t="n">
-        <v>0.1853922696909436</v>
+        <v>0.1841347438078316</v>
       </c>
     </row>
     <row r="28">
@@ -3911,37 +4328,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1640</v>
+        <v>1340</v>
       </c>
       <c r="D28" t="n">
-        <v>54.93666666666667</v>
+        <v>44.94333333333334</v>
       </c>
       <c r="E28" t="n">
-        <v>6.613</v>
+        <v>6.675000000000011</v>
       </c>
       <c r="F28" t="n">
-        <v>294.1908725605803</v>
+        <v>294.1677991825377</v>
       </c>
       <c r="G28" t="n">
-        <v>2.247860357611278</v>
+        <v>2.269113077144798</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>54.87984217671682</v>
+        <v>44.87580165150298</v>
       </c>
       <c r="J28" t="n">
         <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>0.05682448994984668</v>
+        <v>0.06753168183035996</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1016666666666666</v>
+        <v>0.1049999999999969</v>
       </c>
       <c r="N28" t="b">
         <v>0</v>
@@ -3950,25 +4367,25 @@
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>0.06207670532109688</v>
+        <v>0.05389935763220421</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.1000000000000014</v>
+        <v>0.09833333333333627</v>
       </c>
       <c r="S28" t="b">
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>55.06085729759004</v>
+        <v>45.06119392119393</v>
       </c>
       <c r="U28" t="n">
         <v>6</v>
       </c>
       <c r="V28" t="n">
-        <v>0.1810151208732194</v>
+        <v>0.1853922696909436</v>
       </c>
     </row>
     <row r="29">
@@ -3981,37 +4398,37 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1940</v>
+        <v>1640</v>
       </c>
       <c r="D29" t="n">
-        <v>64.94</v>
+        <v>54.93666666666667</v>
       </c>
       <c r="E29" t="n">
-        <v>6.744799999999998</v>
+        <v>6.613</v>
       </c>
       <c r="F29" t="n">
-        <v>294.1102572478565</v>
+        <v>294.1908725605803</v>
       </c>
       <c r="G29" t="n">
-        <v>2.293289619721059</v>
+        <v>2.247860357611278</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>64.87544567409766</v>
+        <v>54.87984217671682</v>
       </c>
       <c r="J29" t="n">
         <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>0.06455432590233556</v>
+        <v>0.05682448994984668</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.09833333333332916</v>
+        <v>0.1016666666666666</v>
       </c>
       <c r="N29" t="b">
         <v>0</v>
@@ -4020,24 +4437,94 @@
         <v>2</v>
       </c>
       <c r="P29" t="n">
-        <v>0.05568519369163027</v>
+        <v>0.06207670532109688</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0.1016666666666595</v>
+        <v>0.1000000000000014</v>
       </c>
       <c r="S29" t="b">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>65.05270866845399</v>
+        <v>55.06085729759004</v>
       </c>
       <c r="U29" t="n">
         <v>6</v>
       </c>
       <c r="V29" t="n">
+        <v>0.1810151208732194</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1940</v>
+      </c>
+      <c r="D30" t="n">
+        <v>64.94</v>
+      </c>
+      <c r="E30" t="n">
+        <v>6.744799999999998</v>
+      </c>
+      <c r="F30" t="n">
+        <v>294.1102572478565</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.293289619721059</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>64.87544567409766</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.06455432590233556</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.09833333333332916</v>
+      </c>
+      <c r="N30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.05568519369163027</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.1016666666666595</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>65.05270866845399</v>
+      </c>
+      <c r="U30" t="n">
+        <v>6</v>
+      </c>
+      <c r="V30" t="n">
         <v>0.177262994356326</v>
       </c>
     </row>

--- a/data/processed_data/Video_prueba/contracciones.xlsx
+++ b/data/processed_data/Video_prueba/contracciones.xlsx
@@ -27,16 +27,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -47,7 +44,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -55,21 +52,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,22 +427,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>umbral_px</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>eventos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>falsos_control</t>
         </is>
@@ -797,117 +785,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>frame_pico</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>grosor_reposo_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>meseta_pico_frames</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>onset_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_frames</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_min_s</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ttp_max_s</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ttp_medible</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_frames</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_min_s</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_max_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_medible</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>offset_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>duracion_frames</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
@@ -3045,112 +3033,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
@@ -3365,321 +3353,326 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK2"/>
+  <dimension ref="A1:BL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_frames</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>signo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ruido_canal_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ruido_grosor_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>k_usado</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>k_automatico</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>hay_meseta</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>meseta_motivo</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>meseta_k_rango</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>conteo_reportable</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>amplitud_traslacion_px</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ritmo</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>fps_medido</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>adelgazamiento_px</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>adelgazamiento_sigma</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>retardo_adelgazamiento_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cociente_adelg_trasl_pct</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_px</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_sigma</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>cociente_robusto_pct</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>blur_px</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>blur_sigma</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>cinetica_grupo_principal</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>eventos_junto_al_borde</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>mesetas</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ruido_borde_sup_px</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>ruido_borde_inf_px</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>cociente_ruido_bordes</t>
         </is>
@@ -3899,35 +3892,38 @@
       <c r="BB2" t="n">
         <v>2</v>
       </c>
-      <c r="BC2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BD2" t="n">
+      <c r="BC2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="n">
         <v>0.2333333333333201</v>
       </c>
-      <c r="BE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="inlineStr">
         <is>
           <t>1.5 s: 29 | 2 s: 29 | 3 s: 29</t>
         </is>
       </c>
-      <c r="BG2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BH2" t="inlineStr">
+      <c r="BH2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BI2" t="inlineStr">
         <is>
           <t>29 ev en k=5.315-15.163</t>
         </is>
       </c>
-      <c r="BI2" t="n">
+      <c r="BJ2" t="n">
         <v>0.1095641400000554</v>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BK2" t="n">
         <v>0.08569428000006364</v>
       </c>
-      <c r="BK2" t="n">
+      <c r="BL2" t="n">
         <v>1.278546712802465</v>
       </c>
     </row>
@@ -3946,52 +3942,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_inicio_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_fin_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>intervalo_IQR_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>frecuencia_mediana_Hz</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>CV_intervalo_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>amplitud_mediana_px</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>amplitud_IQR_px</t>
         </is>
@@ -4080,87 +4076,87 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>busqueda</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>veredicto</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>clasificacion</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>periodo_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>periodo_err_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>frecuencia_Hz</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>jitter_ms</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>p_valor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>n_eventos_tren</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>n_ranuras</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>captura_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>n_dudosos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>n_sacados_tiempo_amplitud</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inicio_s</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>fin_s</t>
         </is>
@@ -4240,32 +4236,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>indice_evento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>desvio_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>amplitud</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>amplitud_mediana_tren</t>
         </is>
@@ -4306,32 +4302,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ranura</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_esperado_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_medido_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>error_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>capturada</t>
         </is>
@@ -4472,17 +4468,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>intervalo_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>frecuencia_Hz</t>
         </is>
@@ -4745,37 +4741,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>amplitud_mediana_px</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>frecuencia_Hz</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>t_inicio_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>t_fin_s</t>
         </is>
@@ -4842,28 +4838,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>junto_a_hueco</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>junto_al_borde</t>
         </is>
       </c>
     </row>
@@ -4880,6 +4881,9 @@
       <c r="D2" t="b">
         <v>0</v>
       </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -4893,6 +4897,9 @@
       </c>
       <c r="D3" t="b">
         <v>0</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -4908,6 +4915,9 @@
       <c r="D4" t="b">
         <v>0</v>
       </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -4922,6 +4932,9 @@
       <c r="D5" t="b">
         <v>0</v>
       </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4936,6 +4949,9 @@
       <c r="D6" t="b">
         <v>0</v>
       </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4950,6 +4966,9 @@
       <c r="D7" t="b">
         <v>0</v>
       </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4964,6 +4983,9 @@
       <c r="D8" t="b">
         <v>0</v>
       </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4978,6 +5000,9 @@
       <c r="D9" t="b">
         <v>0</v>
       </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4992,6 +5017,9 @@
       <c r="D10" t="b">
         <v>0</v>
       </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -5006,6 +5034,9 @@
       <c r="D11" t="b">
         <v>0</v>
       </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -5020,6 +5051,9 @@
       <c r="D12" t="b">
         <v>0</v>
       </c>
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -5034,6 +5068,9 @@
       <c r="D13" t="b">
         <v>0</v>
       </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -5048,6 +5085,9 @@
       <c r="D14" t="b">
         <v>0</v>
       </c>
+      <c r="E14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -5062,6 +5102,9 @@
       <c r="D15" t="b">
         <v>0</v>
       </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5076,6 +5119,9 @@
       <c r="D16" t="b">
         <v>0</v>
       </c>
+      <c r="E16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -5090,6 +5136,9 @@
       <c r="D17" t="b">
         <v>0</v>
       </c>
+      <c r="E17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -5104,6 +5153,9 @@
       <c r="D18" t="b">
         <v>0</v>
       </c>
+      <c r="E18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -5118,6 +5170,9 @@
       <c r="D19" t="b">
         <v>0</v>
       </c>
+      <c r="E19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -5132,6 +5187,9 @@
       <c r="D20" t="b">
         <v>0</v>
       </c>
+      <c r="E20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5146,6 +5204,9 @@
       <c r="D21" t="b">
         <v>0</v>
       </c>
+      <c r="E21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5160,6 +5221,9 @@
       <c r="D22" t="b">
         <v>0</v>
       </c>
+      <c r="E22" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -5174,6 +5238,9 @@
       <c r="D23" t="b">
         <v>0</v>
       </c>
+      <c r="E23" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5188,6 +5255,9 @@
       <c r="D24" t="b">
         <v>0</v>
       </c>
+      <c r="E24" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -5202,6 +5272,9 @@
       <c r="D25" t="b">
         <v>0</v>
       </c>
+      <c r="E25" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -5216,6 +5289,9 @@
       <c r="D26" t="b">
         <v>0</v>
       </c>
+      <c r="E26" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -5230,6 +5306,9 @@
       <c r="D27" t="b">
         <v>0</v>
       </c>
+      <c r="E27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -5244,6 +5323,9 @@
       <c r="D28" t="b">
         <v>0</v>
       </c>
+      <c r="E28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -5258,6 +5340,9 @@
       <c r="D29" t="b">
         <v>0</v>
       </c>
+      <c r="E29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -5270,6 +5355,9 @@
         <v>6.744799999999998</v>
       </c>
       <c r="D30" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" t="b">
         <v>0</v>
       </c>
     </row>
